--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_GRUPO URETA TIZONA BURGOS.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_GRUPO URETA TIZONA BURGOS.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>J. ZIDEK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>41.9016</v>
+        <v>37.4756</v>
       </c>
       <c r="E2" t="n">
-        <v>50.4502</v>
+        <v>46.5422</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.5489</v>
+        <v>-9.066800000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>29.2666</v>
+        <v>14.9234</v>
       </c>
       <c r="H2" t="n">
-        <v>30.717</v>
+        <v>6.3123</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.45</v>
+        <v>8.611000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>50.7456</v>
+        <v>47.5942</v>
       </c>
       <c r="K2" t="n">
-        <v>40.38</v>
+        <v>21.5744</v>
       </c>
       <c r="L2" t="n">
-        <v>10.3649</v>
+        <v>26.0196</v>
       </c>
       <c r="M2" t="n">
-        <v>-21.4788</v>
+        <v>-32.6708</v>
       </c>
       <c r="N2" t="n">
-        <v>-9.6631</v>
+        <v>-15.2616</v>
       </c>
       <c r="O2" t="n">
-        <v>-11.8154</v>
+        <v>-17.4088</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.610400000000001</v>
+        <v>5.2201</v>
       </c>
       <c r="Q2" t="n">
-        <v>-35.8884</v>
+        <v>-30.6682</v>
       </c>
       <c r="R2" t="n">
-        <v>33.2779</v>
+        <v>35.8883</v>
       </c>
       <c r="S2" t="n">
-        <v>25.9061</v>
+        <v>-2.722</v>
       </c>
       <c r="T2" t="n">
-        <v>22.2172</v>
+        <v>0.5244999999999997</v>
       </c>
       <c r="U2" t="n">
-        <v>3.6883</v>
+        <v>-3.2463</v>
       </c>
       <c r="V2" t="n">
-        <v>-10.6609</v>
+        <v>20.0537</v>
       </c>
       <c r="W2" t="n">
-        <v>13.3764</v>
+        <v>29.0922</v>
       </c>
       <c r="X2" t="n">
-        <v>-24.0368</v>
+        <v>-9.038499999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ZIDEK</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>35.1932</v>
+        <v>24.9022</v>
       </c>
       <c r="E3" t="n">
-        <v>48.0058</v>
+        <v>35.6438</v>
       </c>
       <c r="F3" t="n">
-        <v>-12.812</v>
+        <v>-10.7416</v>
       </c>
       <c r="G3" t="n">
-        <v>14.9234</v>
+        <v>29.2666</v>
       </c>
       <c r="H3" t="n">
-        <v>6.3123</v>
+        <v>30.717</v>
       </c>
       <c r="I3" t="n">
-        <v>8.611000000000001</v>
+        <v>-1.45</v>
       </c>
       <c r="J3" t="n">
-        <v>47.5942</v>
+        <v>50.7456</v>
       </c>
       <c r="K3" t="n">
-        <v>21.5744</v>
+        <v>40.38</v>
       </c>
       <c r="L3" t="n">
-        <v>26.0196</v>
+        <v>10.3649</v>
       </c>
       <c r="M3" t="n">
-        <v>-32.6708</v>
+        <v>-21.4788</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.2616</v>
+        <v>-9.6631</v>
       </c>
       <c r="O3" t="n">
-        <v>-17.4088</v>
+        <v>-11.8154</v>
       </c>
       <c r="P3" t="n">
-        <v>5.2201</v>
+        <v>-2.610400000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-30.6682</v>
+        <v>-35.8884</v>
       </c>
       <c r="R3" t="n">
-        <v>35.8883</v>
+        <v>33.2779</v>
       </c>
       <c r="S3" t="n">
-        <v>-5.004</v>
+        <v>8.9064</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9877</v>
+        <v>7.4108</v>
       </c>
       <c r="U3" t="n">
-        <v>-6.9917</v>
+        <v>1.4954</v>
       </c>
       <c r="V3" t="n">
-        <v>20.0537</v>
+        <v>-10.6609</v>
       </c>
       <c r="W3" t="n">
-        <v>29.0922</v>
+        <v>13.3764</v>
       </c>
       <c r="X3" t="n">
-        <v>-9.038499999999999</v>
+        <v>-24.0368</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>6.5074</v>
+        <v>9.234900000000003</v>
       </c>
       <c r="E4" t="n">
-        <v>31.5967</v>
+        <v>24.8095</v>
       </c>
       <c r="F4" t="n">
-        <v>-25.0895</v>
+        <v>-15.5743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.911300000000001</v>
+        <v>24.573</v>
       </c>
       <c r="H4" t="n">
-        <v>8.882</v>
+        <v>5.3847</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.971200000000001</v>
+        <v>19.1887</v>
       </c>
       <c r="J4" t="n">
-        <v>44.7785</v>
+        <v>52.3895</v>
       </c>
       <c r="K4" t="n">
-        <v>28.0872</v>
+        <v>18.803</v>
       </c>
       <c r="L4" t="n">
-        <v>16.6911</v>
+        <v>33.5867</v>
       </c>
       <c r="M4" t="n">
-        <v>-39.8667</v>
+        <v>-27.8167</v>
       </c>
       <c r="N4" t="n">
-        <v>-19.2045</v>
+        <v>-13.4188</v>
       </c>
       <c r="O4" t="n">
-        <v>-20.6622</v>
+        <v>-14.3979</v>
       </c>
       <c r="P4" t="n">
-        <v>9.1349</v>
+        <v>-21.098</v>
       </c>
       <c r="Q4" t="n">
-        <v>-38.2808</v>
+        <v>-55.899</v>
       </c>
       <c r="R4" t="n">
-        <v>47.4163</v>
+        <v>34.8005</v>
       </c>
       <c r="S4" t="n">
-        <v>7.7666</v>
+        <v>3.0898</v>
       </c>
       <c r="T4" t="n">
-        <v>11.2002</v>
+        <v>1.333</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.4332</v>
+        <v>1.7565</v>
       </c>
       <c r="V4" t="n">
-        <v>-15.3061</v>
+        <v>2.6704</v>
       </c>
       <c r="W4" t="n">
-        <v>13.8995</v>
+        <v>26.9864</v>
       </c>
       <c r="X4" t="n">
-        <v>-29.2057</v>
+        <v>-24.3157</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.701800000000001</v>
+        <v>4.555599999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>16.842</v>
+        <v>26.701</v>
       </c>
       <c r="F5" t="n">
-        <v>-18.5441</v>
+        <v>-22.1458</v>
       </c>
       <c r="G5" t="n">
-        <v>24.573</v>
+        <v>4.911300000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3847</v>
+        <v>8.882</v>
       </c>
       <c r="I5" t="n">
-        <v>19.1887</v>
+        <v>-3.971200000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>52.3895</v>
+        <v>44.7785</v>
       </c>
       <c r="K5" t="n">
-        <v>18.803</v>
+        <v>28.0872</v>
       </c>
       <c r="L5" t="n">
-        <v>33.5867</v>
+        <v>16.6911</v>
       </c>
       <c r="M5" t="n">
-        <v>-27.8167</v>
+        <v>-39.8667</v>
       </c>
       <c r="N5" t="n">
-        <v>-13.4188</v>
+        <v>-19.2045</v>
       </c>
       <c r="O5" t="n">
-        <v>-14.3979</v>
+        <v>-20.6622</v>
       </c>
       <c r="P5" t="n">
-        <v>-21.098</v>
+        <v>9.1349</v>
       </c>
       <c r="Q5" t="n">
-        <v>-55.899</v>
+        <v>-38.2808</v>
       </c>
       <c r="R5" t="n">
-        <v>34.8005</v>
+        <v>47.4163</v>
       </c>
       <c r="S5" t="n">
-        <v>-7.8473</v>
+        <v>5.8153</v>
       </c>
       <c r="T5" t="n">
-        <v>-6.634300000000001</v>
+        <v>6.3041</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.213</v>
+        <v>-0.4893</v>
       </c>
       <c r="V5" t="n">
-        <v>2.6704</v>
+        <v>-15.3061</v>
       </c>
       <c r="W5" t="n">
-        <v>26.9864</v>
+        <v>13.8995</v>
       </c>
       <c r="X5" t="n">
-        <v>-24.3157</v>
+        <v>-29.2057</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. CZERAPOWICZ</t>
+          <t>M. JACKSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>-9.667299999999999</v>
+        <v>-2.078699999999997</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.143</v>
+        <v>31.0434</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5244</v>
+        <v>-33.1219</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.9033</v>
+        <v>-0.2306999999999997</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.907</v>
+        <v>-14.6628</v>
       </c>
       <c r="I6" t="n">
-        <v>-6.9964</v>
+        <v>14.4323</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.1706</v>
+        <v>50.0843</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7617</v>
+        <v>10.1454</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.9322</v>
+        <v>39.9388</v>
       </c>
       <c r="M6" t="n">
-        <v>-6.732800000000001</v>
+        <v>-50.3148</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.6686</v>
+        <v>-24.8082</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.064100000000001</v>
+        <v>-25.5068</v>
       </c>
       <c r="P6" t="n">
-        <v>4.3501</v>
+        <v>11.7452</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.785</v>
+        <v>-40.2383</v>
       </c>
       <c r="R6" t="n">
-        <v>9.135199999999999</v>
+        <v>51.9842</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8440999999999999</v>
+        <v>-4.7114</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2077000000000001</v>
+        <v>-0.7447</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0518</v>
+        <v>-3.9668</v>
       </c>
       <c r="V6" t="n">
-        <v>-5.9581</v>
+        <v>-8.8818</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02069999999999983</v>
+        <v>21.9427</v>
       </c>
       <c r="X6" t="n">
-        <v>-5.9786</v>
+        <v>-30.8247</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>-9.9824</v>
+        <v>-6.4146</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.673500000000001</v>
+        <v>-2.431000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.3092</v>
+        <v>-3.9835</v>
       </c>
       <c r="G7" t="n">
         <v>8.997800000000002</v>
@@ -1000,13 +1000,13 @@
         <v>13.4855</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.323</v>
+        <v>-1.7551</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.3553</v>
+        <v>-0.1130000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.9679</v>
+        <v>-1.6423</v>
       </c>
       <c r="V7" t="n">
         <v>-8.0022</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ALONSO CUEVAS</t>
+          <t>A. ALONSO RUIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>-10.6979</v>
+        <v>-7.7851</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4985999999999997</v>
+        <v>2.7601</v>
       </c>
       <c r="F8" t="n">
-        <v>-10.1995</v>
+        <v>-10.5453</v>
       </c>
       <c r="G8" t="n">
-        <v>-10.3854</v>
+        <v>13.8113</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9041999999999999</v>
+        <v>6.4899</v>
       </c>
       <c r="I8" t="n">
-        <v>-11.2897</v>
+        <v>7.321499999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>10.1214</v>
+        <v>30.0239</v>
       </c>
       <c r="K8" t="n">
-        <v>10.8588</v>
+        <v>15.4181</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7373999999999998</v>
+        <v>14.6055</v>
       </c>
       <c r="M8" t="n">
-        <v>-20.5071</v>
+        <v>-16.2127</v>
       </c>
       <c r="N8" t="n">
-        <v>-9.9549</v>
+        <v>-8.9284</v>
       </c>
       <c r="O8" t="n">
-        <v>-10.5523</v>
+        <v>-7.2847</v>
       </c>
       <c r="P8" t="n">
-        <v>1.305</v>
+        <v>-9.570699999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-18.2702</v>
+        <v>-37.1935</v>
       </c>
       <c r="R8" t="n">
-        <v>19.5752</v>
+        <v>27.6228</v>
       </c>
       <c r="S8" t="n">
-        <v>7.2686</v>
+        <v>-1.2729</v>
       </c>
       <c r="T8" t="n">
-        <v>4.2192</v>
+        <v>-1.3193</v>
       </c>
       <c r="U8" t="n">
-        <v>3.0492</v>
+        <v>0.0465000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-8.885899999999999</v>
+        <v>-10.7531</v>
       </c>
       <c r="W8" t="n">
-        <v>3.4312</v>
+        <v>11.2494</v>
       </c>
       <c r="X8" t="n">
-        <v>-12.3172</v>
+        <v>-22.0024</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ALONSO RUIZ</t>
+          <t>G. JOFRESA SARRET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>-16.0123</v>
+        <v>-10.2658</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4202</v>
+        <v>2.680399999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-13.5921</v>
+        <v>-12.9458</v>
       </c>
       <c r="G9" t="n">
-        <v>13.8113</v>
+        <v>-17.865</v>
       </c>
       <c r="H9" t="n">
-        <v>6.4899</v>
+        <v>-12.5108</v>
       </c>
       <c r="I9" t="n">
-        <v>7.321499999999999</v>
+        <v>-5.354199999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>30.0239</v>
+        <v>14.556</v>
       </c>
       <c r="K9" t="n">
-        <v>15.4181</v>
+        <v>4.4738</v>
       </c>
       <c r="L9" t="n">
-        <v>14.6055</v>
+        <v>10.0824</v>
       </c>
       <c r="M9" t="n">
-        <v>-16.2127</v>
+        <v>-32.4211</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.9284</v>
+        <v>-16.9848</v>
       </c>
       <c r="O9" t="n">
-        <v>-7.2847</v>
+        <v>-15.4363</v>
       </c>
       <c r="P9" t="n">
-        <v>-9.570699999999999</v>
+        <v>-4.7852</v>
       </c>
       <c r="Q9" t="n">
-        <v>-37.1935</v>
+        <v>-45.8936</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6228</v>
+        <v>41.1083</v>
       </c>
       <c r="S9" t="n">
-        <v>-9.5001</v>
+        <v>-3.0238</v>
       </c>
       <c r="T9" t="n">
-        <v>-6.500100000000001</v>
+        <v>-0.3337000000000003</v>
       </c>
       <c r="U9" t="n">
-        <v>-3.0001</v>
+        <v>-2.69</v>
       </c>
       <c r="V9" t="n">
-        <v>-10.7531</v>
+        <v>15.4083</v>
       </c>
       <c r="W9" t="n">
-        <v>11.2494</v>
+        <v>34.3517</v>
       </c>
       <c r="X9" t="n">
-        <v>-22.0024</v>
+        <v>-18.9433</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. JOFRESA SARRET</t>
+          <t>C. CZERAPOWICZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>-20.4806</v>
+        <v>-10.9098</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.957699999999997</v>
+        <v>-7.2655</v>
       </c>
       <c r="F10" t="n">
-        <v>-14.5229</v>
+        <v>-3.6442</v>
       </c>
       <c r="G10" t="n">
-        <v>-17.865</v>
+        <v>-8.9033</v>
       </c>
       <c r="H10" t="n">
-        <v>-12.5108</v>
+        <v>-1.907</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.354199999999999</v>
+        <v>-6.9964</v>
       </c>
       <c r="J10" t="n">
-        <v>14.556</v>
+        <v>-2.1706</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4738</v>
+        <v>0.7617</v>
       </c>
       <c r="L10" t="n">
-        <v>10.0824</v>
+        <v>-2.9322</v>
       </c>
       <c r="M10" t="n">
-        <v>-32.4211</v>
+        <v>-6.732800000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-16.9848</v>
+        <v>-2.6686</v>
       </c>
       <c r="O10" t="n">
-        <v>-15.4363</v>
+        <v>-4.064100000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.7852</v>
+        <v>4.3501</v>
       </c>
       <c r="Q10" t="n">
-        <v>-45.8936</v>
+        <v>-4.785</v>
       </c>
       <c r="R10" t="n">
-        <v>41.1083</v>
+        <v>9.135199999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-13.2393</v>
+        <v>-0.3982999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-8.972</v>
+        <v>-0.3304</v>
       </c>
       <c r="U10" t="n">
-        <v>-4.2679</v>
+        <v>-0.06790000000000007</v>
       </c>
       <c r="V10" t="n">
-        <v>15.4083</v>
+        <v>-5.9581</v>
       </c>
       <c r="W10" t="n">
-        <v>34.3517</v>
+        <v>0.02069999999999983</v>
       </c>
       <c r="X10" t="n">
-        <v>-18.9433</v>
+        <v>-5.9786</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. JACKSON</t>
+          <t>A. ALONSO CUEVAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>-20.8823</v>
+        <v>-11.4939</v>
       </c>
       <c r="E11" t="n">
-        <v>19.8892</v>
+        <v>-0.5344000000000007</v>
       </c>
       <c r="F11" t="n">
-        <v>-40.7714</v>
+        <v>-10.9598</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2306999999999997</v>
+        <v>-10.3854</v>
       </c>
       <c r="H11" t="n">
-        <v>-14.6628</v>
+        <v>0.9041999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>14.4323</v>
+        <v>-11.2897</v>
       </c>
       <c r="J11" t="n">
-        <v>50.0843</v>
+        <v>10.1214</v>
       </c>
       <c r="K11" t="n">
-        <v>10.1454</v>
+        <v>10.8588</v>
       </c>
       <c r="L11" t="n">
-        <v>39.9388</v>
+        <v>-0.7373999999999998</v>
       </c>
       <c r="M11" t="n">
-        <v>-50.3148</v>
+        <v>-20.5071</v>
       </c>
       <c r="N11" t="n">
-        <v>-24.8082</v>
+        <v>-9.9549</v>
       </c>
       <c r="O11" t="n">
-        <v>-25.5068</v>
+        <v>-10.5523</v>
       </c>
       <c r="P11" t="n">
-        <v>11.7452</v>
+        <v>1.305</v>
       </c>
       <c r="Q11" t="n">
-        <v>-40.2383</v>
+        <v>-18.2702</v>
       </c>
       <c r="R11" t="n">
-        <v>51.9842</v>
+        <v>19.5752</v>
       </c>
       <c r="S11" t="n">
-        <v>-23.5153</v>
+        <v>6.472300000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-11.899</v>
+        <v>4.1831</v>
       </c>
       <c r="U11" t="n">
-        <v>-11.6167</v>
+        <v>2.2891</v>
       </c>
       <c r="V11" t="n">
-        <v>-8.8818</v>
+        <v>-8.885899999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>21.9427</v>
+        <v>3.4312</v>
       </c>
       <c r="X11" t="n">
-        <v>-30.8247</v>
+        <v>-12.3172</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>28</v>
       </c>
       <c r="D12" t="n">
-        <v>-26.085</v>
+        <v>-21.6687</v>
       </c>
       <c r="E12" t="n">
-        <v>-16.719</v>
+        <v>-14.5881</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.3666</v>
+        <v>-7.0804</v>
       </c>
       <c r="G12" t="n">
         <v>-15.5762</v>
@@ -1390,13 +1390,13 @@
         <v>26.5354</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.3276</v>
+        <v>1.0894</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8675</v>
+        <v>2.9983</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.1952</v>
+        <v>-1.9091</v>
       </c>
       <c r="V12" t="n">
         <v>0.648400000000001</v>
@@ -1423,13 +1423,13 @@
         <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-32.689</v>
+        <v>-34.4037</v>
       </c>
       <c r="E13" t="n">
-        <v>-16.5859</v>
+        <v>-17.4223</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.1032</v>
+        <v>-16.9812</v>
       </c>
       <c r="G13" t="n">
         <v>-22.2814</v>
@@ -1468,13 +1468,13 @@
         <v>31.3205</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5964</v>
+        <v>1.882</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8009</v>
+        <v>2.9646</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2046999999999997</v>
+        <v>-1.0829</v>
       </c>
       <c r="V13" t="n">
         <v>-19.442</v>
@@ -1501,13 +1501,13 @@
         <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>-42.9975</v>
+        <v>-40.5191</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.1788</v>
+        <v>-14.7356</v>
       </c>
       <c r="F14" t="n">
-        <v>-27.8184</v>
+        <v>-25.7837</v>
       </c>
       <c r="G14" t="n">
         <v>-37.5935</v>
@@ -1546,13 +1546,13 @@
         <v>40.2383</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.059699999999999</v>
+        <v>0.4181</v>
       </c>
       <c r="T14" t="n">
-        <v>1.841399999999999</v>
+        <v>2.2848</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.9016</v>
+        <v>-1.8667</v>
       </c>
       <c r="V14" t="n">
         <v>-12.4794</v>
@@ -1579,13 +1579,13 @@
         <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>-60.42290000000001</v>
+        <v>-71.518</v>
       </c>
       <c r="E15" t="n">
-        <v>-51.8745</v>
+        <v>-58.223</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.548299999999999</v>
+        <v>-13.2949</v>
       </c>
       <c r="G15" t="n">
         <v>-46.04940000000001</v>
@@ -1624,13 +1624,13 @@
         <v>46.5459</v>
       </c>
       <c r="S15" t="n">
-        <v>24.6692</v>
+        <v>13.574</v>
       </c>
       <c r="T15" t="n">
-        <v>14.5538</v>
+        <v>8.205299999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>10.1151</v>
+        <v>5.3686</v>
       </c>
       <c r="V15" t="n">
         <v>-4.024199999999999</v>
@@ -1657,13 +1657,13 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>-168.0168</v>
+        <v>-140.8891</v>
       </c>
       <c r="E16" t="n">
-        <v>45.73270000000002</v>
+        <v>54.98049999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-213.7505</v>
+        <v>-195.8692</v>
       </c>
       <c r="G16" t="n">
         <v>-62.4015</v>
@@ -1702,13 +1702,13 @@
         <v>458.9343</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2347000000000037</v>
+        <v>27.3638</v>
       </c>
       <c r="T16" t="n">
-        <v>24.1195</v>
+        <v>33.3674</v>
       </c>
       <c r="U16" t="n">
-        <v>-23.8876</v>
+        <v>-6.005200000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-65.6129</v>
